--- a/public/templates/products-template.xlsx
+++ b/public/templates/products-template.xlsx
@@ -1,134 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\projectpvc\pvc\public\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3CB6AB-C56D-42A7-9001-45B50B5F76B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="18250" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>nama_produk</t>
-  </si>
-  <si>
-    <t>kategori_kode</t>
-  </si>
-  <si>
-    <t>satuan_kode</t>
-  </si>
-  <si>
-    <t>hpp</t>
-  </si>
-  <si>
-    <t>stok_awal</t>
-  </si>
-  <si>
-    <t>barcode</t>
-  </si>
-  <si>
-    <t>panjang_cm</t>
-  </si>
-  <si>
-    <t>lebar_mm</t>
-  </si>
-  <si>
-    <t>tebal_mm</t>
-  </si>
-  <si>
-    <t>catatan</t>
-  </si>
-  <si>
-    <t>PVC-001</t>
-  </si>
-  <si>
-    <t>Papan PVC Glossy Putih</t>
-  </si>
-  <si>
-    <t>PVC</t>
-  </si>
-  <si>
-    <t>PCS</t>
-  </si>
-  <si>
-    <t>8991234567890</t>
-  </si>
-  <si>
-    <t>LIS-001</t>
-  </si>
-  <si>
-    <t>Lis Figura Emas 3cm</t>
-  </si>
-  <si>
-    <t>LIS</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>Hati-hati saat memotong</t>
-  </si>
-  <si>
-    <t>ROL-001</t>
-  </si>
-  <si>
-    <t>Wallpaper Vinyl Roll</t>
-  </si>
-  <si>
-    <t>WLP</t>
-  </si>
-  <si>
-    <t>ROLL</t>
-  </si>
-  <si>
-    <t>8991234567891</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -140,43 +53,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -464,153 +428,318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.453125" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>nama_produk</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>kategori_kode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>satuan_kode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>hpp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>stok_awal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>panjang_cm</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lebar_mm</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tebal_mm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>catatan</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pattern_code</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>finish</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>harga_jual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PVC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Papan PVC Glossy Putih</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>8991234567890</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Glossy</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>GP-001</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Glossy</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LIS-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Lis Figura Emas 3cm</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>LIS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Hati-hati saat memotong</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Figura</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>FG-001</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>18000</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>55000</v>
-      </c>
-      <c r="F2">
-        <v>150</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>240</v>
-      </c>
-      <c r="I2">
-        <v>20</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3">
-        <v>12500</v>
-      </c>
-      <c r="F3">
-        <v>300</v>
-      </c>
-      <c r="H3">
-        <v>400</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ROL-001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Wallpaper Vinyl Roll</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>WLP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ROLL</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>150000</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8991234567891</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Vinyl</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Wallpaper</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>WP-001</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Matte</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>220000</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Satuan Tidak Valid" error="Pilih satuan yang valid" type="list">
+      <formula1>"PCS,MTR,M,ROLL,BOX,SET,LUSIN"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>